--- a/Team-Data/2013-14/11-19-2013-14.xlsx
+++ b/Team-Data/2013-14/11-19-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.545</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>38.5</v>
+        <v>39.1</v>
       </c>
       <c r="J2" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
-        <v>0.474</v>
+        <v>0.477</v>
       </c>
       <c r="L2" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.358</v>
       </c>
       <c r="O2" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="P2" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R2" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="S2" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="V2" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="W2" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y2" t="n">
         <v>3.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.2</v>
+        <v>104.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,67 +821,67 @@
         <v>14</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
         <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -843,94 +910,94 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.439</v>
+        <v>0.452</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.321</v>
+        <v>0.317</v>
       </c>
       <c r="O3" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P3" t="n">
         <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.764</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="S3" t="n">
-        <v>30.1</v>
+        <v>30.5</v>
       </c>
       <c r="T3" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U3" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="V3" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>93.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>14</v>
@@ -939,16 +1006,16 @@
         <v>20</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
         <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN3" t="n">
         <v>27</v>
@@ -960,43 +1027,43 @@
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU3" t="n">
         <v>28</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -1103,46 +1170,46 @@
         <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
         <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
@@ -1151,19 +1218,19 @@
         <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>14</v>
@@ -1324,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>16</v>
@@ -1348,10 +1415,10 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1488,7 +1555,7 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>27</v>
@@ -1521,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
         <v>24</v>
@@ -1533,13 +1600,13 @@
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>14</v>
       </c>
       <c r="BB6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1716,25 @@
         <v>-7</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>18</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1682,22 +1749,22 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>25</v>
       </c>
       <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
         <v>12</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
       </c>
       <c r="AS7" t="n">
         <v>18</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="n">
         <v>26</v>
@@ -1709,13 +1776,13 @@
         <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1861,10 +1928,10 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
@@ -1873,7 +1940,7 @@
         <v>5</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
         <v>18</v>
@@ -1897,10 +1964,10 @@
         <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2034,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>14</v>
@@ -2049,16 +2116,16 @@
         <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
@@ -2085,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2117,106 +2184,106 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>38.1</v>
+        <v>38.4</v>
       </c>
       <c r="J10" t="n">
-        <v>84.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.453</v>
+        <v>0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.289</v>
+        <v>0.281</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P10" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.694</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
         <v>27.1</v>
       </c>
       <c r="T10" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="X10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y10" t="n">
         <v>4.8</v>
       </c>
-      <c r="Y10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Z10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA10" t="n">
         <v>21.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2246,28 +2313,28 @@
         <v>23</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2392,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>23</v>
@@ -2413,7 +2480,7 @@
         <v>26</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ11" t="n">
         <v>21</v>
@@ -2428,13 +2495,13 @@
         <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>7</v>
@@ -2449,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2481,106 +2548,106 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.636</v>
       </c>
       <c r="H12" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="J12" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.477</v>
+        <v>0.469</v>
       </c>
       <c r="L12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>26.1</v>
+        <v>26.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.335</v>
+        <v>0.329</v>
       </c>
       <c r="O12" t="n">
-        <v>26.3</v>
+        <v>27</v>
       </c>
       <c r="P12" t="n">
-        <v>37.5</v>
+        <v>38.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7</v>
+        <v>0.697</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="S12" t="n">
-        <v>36.6</v>
+        <v>36.1</v>
       </c>
       <c r="T12" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="U12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="W12" t="n">
         <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>28.8</v>
+        <v>29.6</v>
       </c>
       <c r="AB12" t="n">
         <v>108.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
         <v>7</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2598,10 +2665,10 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2759,7 +2826,7 @@
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2774,16 +2841,16 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
         <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
@@ -2795,7 +2862,7 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>8</v>
       </c>
       <c r="AG14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
         <v>14</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
@@ -2956,13 +3023,13 @@
         <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
@@ -2977,13 +3044,13 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>8</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="AF15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>16</v>
@@ -3123,16 +3190,16 @@
         <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="n">
         <v>6</v>
@@ -3144,10 +3211,10 @@
         <v>27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3159,7 +3226,7 @@
         <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>18</v>
@@ -3180,7 +3247,7 @@
         <v>16</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>-1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP16" t="n">
         <v>20</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -3391,55 +3458,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="L17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.441</v>
+        <v>0.438</v>
       </c>
       <c r="O17" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.734</v>
+        <v>0.741</v>
       </c>
       <c r="R17" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="U17" t="n">
         <v>26</v>
@@ -3448,43 +3515,43 @@
         <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
         <v>2.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>105.9</v>
+        <v>106.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
         <v>14</v>
       </c>
       <c r="AI17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3505,28 +3572,28 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>15</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -3544,7 +3611,7 @@
         <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH18" t="n">
         <v>14</v>
@@ -3675,7 +3742,7 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM18" t="n">
         <v>22</v>
@@ -3684,7 +3751,7 @@
         <v>5</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3693,13 +3760,13 @@
         <v>4</v>
       </c>
       <c r="AR18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
@@ -3711,16 +3778,16 @@
         <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.583</v>
+        <v>0.636</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="J19" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O19" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.806</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="T19" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="U19" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="X19" t="n">
         <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>107.8</v>
+        <v>108.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH19" t="n">
         <v>11</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>5</v>
@@ -3854,52 +3921,52 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN19" t="n">
         <v>15</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>3</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
         <v>29</v>
       </c>
       <c r="AY19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>8</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
@@ -4030,16 +4097,16 @@
         <v>14</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>30</v>
@@ -4048,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>15</v>
@@ -4057,13 +4124,13 @@
         <v>6</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
@@ -4072,16 +4139,16 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
         <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>84.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K21" t="n">
         <v>0.424</v>
       </c>
       <c r="L21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M21" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
         <v>13.8</v>
@@ -4158,55 +4225,55 @@
         <v>17.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R21" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S21" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="T21" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="U21" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="V21" t="n">
         <v>13.1</v>
       </c>
       <c r="W21" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.5</v>
+        <v>94.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH21" t="n">
         <v>14</v>
@@ -4215,19 +4282,19 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,10 +4303,10 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4251,25 +4318,25 @@
         <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW21" t="n">
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
         <v>28</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4379,28 +4446,28 @@
         <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF22" t="n">
         <v>4</v>
       </c>
       <c r="AG22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ22" t="n">
         <v>17</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
         <v>22</v>
@@ -4451,7 +4518,7 @@
         <v>10</v>
       </c>
       <c r="BB22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>18</v>
@@ -4573,10 +4640,10 @@
         <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
@@ -4597,19 +4664,19 @@
         <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
         <v>22</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS23" t="n">
         <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>16</v>
@@ -4621,7 +4688,7 @@
         <v>21</v>
       </c>
       <c r="AX23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY23" t="n">
         <v>28</v>
@@ -4630,10 +4697,10 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4749,13 +4816,13 @@
         <v>14</v>
       </c>
       <c r="AF24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,16 +4843,16 @@
         <v>20</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS24" t="n">
         <v>9</v>
@@ -4797,10 +4864,10 @@
         <v>11</v>
       </c>
       <c r="AV24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -4815,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -4847,94 +4914,94 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
         <v>37.3</v>
       </c>
       <c r="J25" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="N25" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O25" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="P25" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32.5</v>
+        <v>33.3</v>
       </c>
       <c r="T25" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
-        <v>18.4</v>
+        <v>17.9</v>
       </c>
       <c r="V25" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="W25" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>7</v>
@@ -4949,31 +5016,31 @@
         <v>11</v>
       </c>
       <c r="AL25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN25" t="n">
         <v>14</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
@@ -4982,25 +5049,25 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB25" t="n">
         <v>17</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5125,25 +5192,25 @@
         <v>4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="n">
         <v>9</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AN26" t="n">
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
         <v>10</v>
@@ -5152,7 +5219,7 @@
         <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -5170,13 +5237,13 @@
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>35.3</v>
+        <v>34.9</v>
       </c>
       <c r="J27" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.423</v>
+        <v>0.418</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
         <v>22.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.323</v>
+        <v>0.318</v>
       </c>
       <c r="O27" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="P27" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="S27" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="T27" t="n">
-        <v>40.3</v>
+        <v>39.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="W27" t="n">
         <v>8</v>
@@ -5274,43 +5341,43 @@
         <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>94.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.1</v>
+        <v>-4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
@@ -5319,28 +5386,28 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV27" t="n">
         <v>1</v>
@@ -5352,20 +5419,20 @@
         <v>30</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC27" t="n">
         <v>24</v>
       </c>
-      <c r="BA27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>21</v>
-      </c>
       <c r="BD27" t="n">
         <v>10</v>
       </c>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5522,10 +5589,10 @@
         <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW28" t="n">
         <v>22</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5653,28 +5720,28 @@
         <v>-0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>18</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5689,13 +5756,13 @@
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS29" t="n">
         <v>20</v>
@@ -5707,16 +5774,16 @@
         <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5941,7 @@
         <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5886,7 +5953,7 @@
         <v>19</v>
       </c>
       <c r="AU30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV30" t="n">
         <v>28</v>
@@ -5895,10 +5962,10 @@
         <v>19</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
@@ -5939,94 +6006,94 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="H31" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="I31" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="J31" t="n">
-        <v>87.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.433</v>
+        <v>0.428</v>
       </c>
       <c r="L31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="M31" t="n">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.395</v>
+        <v>0.391</v>
       </c>
       <c r="O31" t="n">
         <v>15</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.714</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="T31" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U31" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="W31" t="n">
         <v>9.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.4</v>
+        <v>100</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.7</v>
+        <v>-4.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -6035,64 +6102,64 @@
         <v>14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS31" t="n">
         <v>23</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-19-2013-14</t>
+          <t>2013-11-19</t>
         </is>
       </c>
     </row>
